--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -23,13 +23,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VFPractitionerCountry</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFPractitionerCountry</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:56:35+00:00</t>
+    <t>2023-11-09T22:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,7 +80,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet VF_PractitionerCountry</t>
+    <t>Use the link in the Expansion section to navigate to the ConceptMap.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,7 +80,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Use the link in the Expansion section to navigate to the ConceptMap.</t>
+    <t>Navigate to the [ConceptMap VF_PractitionerCountry](ConceptMap-CMVFPractitionerCountry.html).</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
+    <sheet name="Include from 200-.1215" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="138">
   <si>
     <t>Property</t>
   </si>
@@ -35,28 +36,28 @@
     <t>Name</t>
   </si>
   <si>
+    <t>VSVFPractitionerCountry</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
     <t>VF_PractitionerCountry</t>
   </si>
   <si>
-    <t>Title</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Navigate to the [ConceptMap VF_PractitionerCountry](ConceptMap-CMVFPractitionerCountry.html).</t>
+    <t>Navigate to [ConceptMap VF_PractitionerCountry](ConceptMap-CMVFPractitionerCountry.html)</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -93,6 +94,339 @@
   </si>
   <si>
     <t>BooleanType[null]</t>
+  </si>
+  <si>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>ALABAMA</t>
+  </si>
+  <si>
+    <t>ALASKA</t>
+  </si>
+  <si>
+    <t>ALBERTA</t>
+  </si>
+  <si>
+    <t>AMERICAN_SAMOA</t>
+  </si>
+  <si>
+    <t>AMERICAN SAMOA</t>
+  </si>
+  <si>
+    <t>ARIZONA</t>
+  </si>
+  <si>
+    <t>ARKANSAS</t>
+  </si>
+  <si>
+    <t>ARMED_FORCES_AF,EU,ME,CA</t>
+  </si>
+  <si>
+    <t>ARMED FORCES AF,EU,ME,CA</t>
+  </si>
+  <si>
+    <t>ARMED_FORCES_AMER_(EXC_CANADA)</t>
+  </si>
+  <si>
+    <t>ARMED FORCES AMER (EXC CANADA)</t>
+  </si>
+  <si>
+    <t>ARMED_FORCES_PACIFIC</t>
+  </si>
+  <si>
+    <t>ARMED FORCES PACIFIC</t>
+  </si>
+  <si>
+    <t>BRITISH_COLUMBIA</t>
+  </si>
+  <si>
+    <t>BRITISH COLUMBIA</t>
+  </si>
+  <si>
+    <t>CALIFORNIA</t>
+  </si>
+  <si>
+    <t>CANADA</t>
+  </si>
+  <si>
+    <t>COLORADO</t>
+  </si>
+  <si>
+    <t>CONNECTICUT</t>
+  </si>
+  <si>
+    <t>DELAWARE</t>
+  </si>
+  <si>
+    <t>DISTRICT_OF_COLUMBIA</t>
+  </si>
+  <si>
+    <t>DISTRICT OF COLUMBIA</t>
+  </si>
+  <si>
+    <t>FEDERATED_STATES_OF_MICRONESIA</t>
+  </si>
+  <si>
+    <t>FEDERATED STATES OF MICRONESIA</t>
+  </si>
+  <si>
+    <t>FLORIDA</t>
+  </si>
+  <si>
+    <t>GEORGIA</t>
+  </si>
+  <si>
+    <t>GUAM</t>
+  </si>
+  <si>
+    <t>HAWAII</t>
+  </si>
+  <si>
+    <t>IDAHO</t>
+  </si>
+  <si>
+    <t>ILLINOIS</t>
+  </si>
+  <si>
+    <t>INDIANA</t>
+  </si>
+  <si>
+    <t>IOWA</t>
+  </si>
+  <si>
+    <t>KANSAS</t>
+  </si>
+  <si>
+    <t>KENTUCKY</t>
+  </si>
+  <si>
+    <t>LOUISIANA</t>
+  </si>
+  <si>
+    <t>MAINE</t>
+  </si>
+  <si>
+    <t>MANITOBA</t>
+  </si>
+  <si>
+    <t>MARSHALL_ISLANDS</t>
+  </si>
+  <si>
+    <t>MARSHALL ISLANDS</t>
+  </si>
+  <si>
+    <t>MARYLAND</t>
+  </si>
+  <si>
+    <t>MASSACHUSETTS</t>
+  </si>
+  <si>
+    <t>MEXICO</t>
+  </si>
+  <si>
+    <t>MICHIGAN</t>
+  </si>
+  <si>
+    <t>MINNESOTA</t>
+  </si>
+  <si>
+    <t>MISSISSIPPI</t>
+  </si>
+  <si>
+    <t>MISSOURI</t>
+  </si>
+  <si>
+    <t>MONTANA</t>
+  </si>
+  <si>
+    <t>NEBRASKA</t>
+  </si>
+  <si>
+    <t>NEVADA</t>
+  </si>
+  <si>
+    <t>NEW_BRUNSWICK</t>
+  </si>
+  <si>
+    <t>NEW BRUNSWICK</t>
+  </si>
+  <si>
+    <t>NEW_HAMPSHIRE</t>
+  </si>
+  <si>
+    <t>NEW HAMPSHIRE</t>
+  </si>
+  <si>
+    <t>NEW_JERSEY</t>
+  </si>
+  <si>
+    <t>NEW JERSEY</t>
+  </si>
+  <si>
+    <t>NEW_MEXICO</t>
+  </si>
+  <si>
+    <t>NEW MEXICO</t>
+  </si>
+  <si>
+    <t>NEW_YORK</t>
+  </si>
+  <si>
+    <t>NEW YORK</t>
+  </si>
+  <si>
+    <t>NEWFOUNDLAND</t>
+  </si>
+  <si>
+    <t>NORTH_CAROLINA</t>
+  </si>
+  <si>
+    <t>NORTH CAROLINA</t>
+  </si>
+  <si>
+    <t>NORTH_DAKOTA</t>
+  </si>
+  <si>
+    <t>NORTH DAKOTA</t>
+  </si>
+  <si>
+    <t>NORTHERN_MARIANA_ISLANDS</t>
+  </si>
+  <si>
+    <t>NORTHERN MARIANA ISLANDS</t>
+  </si>
+  <si>
+    <t>NORTHWEST_TERRITORIES</t>
+  </si>
+  <si>
+    <t>NORTHWEST TERRITORIES</t>
+  </si>
+  <si>
+    <t>NOVA_SCOTIA</t>
+  </si>
+  <si>
+    <t>NOVA SCOTIA</t>
+  </si>
+  <si>
+    <t>NUNAVUT_PROVINCE</t>
+  </si>
+  <si>
+    <t>NUNAVUT PROVINCE</t>
+  </si>
+  <si>
+    <t>OHIO</t>
+  </si>
+  <si>
+    <t>OKLAHOMA</t>
+  </si>
+  <si>
+    <t>ONTARIO</t>
+  </si>
+  <si>
+    <t>OREGON</t>
+  </si>
+  <si>
+    <t>PALAU</t>
+  </si>
+  <si>
+    <t>PENNSYLVANIA</t>
+  </si>
+  <si>
+    <t>PHILIPPINES</t>
+  </si>
+  <si>
+    <t>PRINCE_EDWARD_ISLAND</t>
+  </si>
+  <si>
+    <t>PRINCE EDWARD ISLAND</t>
+  </si>
+  <si>
+    <t>PUERTO_RICO</t>
+  </si>
+  <si>
+    <t>PUERTO RICO</t>
+  </si>
+  <si>
+    <t>QUEBEC</t>
+  </si>
+  <si>
+    <t>RHODE_ISLAND</t>
+  </si>
+  <si>
+    <t>RHODE ISLAND</t>
+  </si>
+  <si>
+    <t>SASKATCHEWAN</t>
+  </si>
+  <si>
+    <t>SOUTH_CAROLINA</t>
+  </si>
+  <si>
+    <t>SOUTH CAROLINA</t>
+  </si>
+  <si>
+    <t>SOUTH_DAKOTA</t>
+  </si>
+  <si>
+    <t>SOUTH DAKOTA</t>
+  </si>
+  <si>
+    <t>TENNESSEE</t>
+  </si>
+  <si>
+    <t>TEXAS</t>
+  </si>
+  <si>
+    <t>U.S._MINOR_OUTLYING_ISLANDS</t>
+  </si>
+  <si>
+    <t>U.S. MINOR OUTLYING ISLANDS</t>
+  </si>
+  <si>
+    <t>UTAH</t>
+  </si>
+  <si>
+    <t>VERMONT</t>
+  </si>
+  <si>
+    <t>VIRGIN_ISLANDS</t>
+  </si>
+  <si>
+    <t>VIRGIN ISLANDS</t>
+  </si>
+  <si>
+    <t>VIRGINIA</t>
+  </si>
+  <si>
+    <t>WASHINGTON</t>
+  </si>
+  <si>
+    <t>WEST_VIRGINIA</t>
+  </si>
+  <si>
+    <t>WEST VIRGINIA</t>
+  </si>
+  <si>
+    <t>WISCONSIN</t>
+  </si>
+  <si>
+    <t>WYOMING</t>
+  </si>
+  <si>
+    <t>YUKON_TERRITORY</t>
+  </si>
+  <si>
+    <t>YUKON TERRITORY</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://va.gov/terminology/vistaDefinedElements/200-.1215</t>
   </si>
 </sst>
 </file>
@@ -270,24 +604,22 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s" s="2">
         <v>12</v>
       </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
@@ -347,6 +679,676 @@
       </c>
       <c r="B15" t="s" s="2">
         <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B82"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="139">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -619,66 +622,68 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -697,658 +702,658 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from 200-.1215" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from unknown" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="162">
   <si>
     <t>Property</t>
   </si>
@@ -30,21 +31,18 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>VSVFPractitionerCountry</t>
+    <t>VF_PractitionerCountry</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>VF_PractitionerCountry</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -60,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -430,6 +428,78 @@
   </si>
   <si>
     <t>http://va.gov/terminology/vistaDefinedElements/200-.1215</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>ASM</t>
+  </si>
+  <si>
+    <t>American Samoa</t>
+  </si>
+  <si>
+    <t>FSM</t>
+  </si>
+  <si>
+    <t>Federated States of Micronesia</t>
+  </si>
+  <si>
+    <t>GUM</t>
+  </si>
+  <si>
+    <t>Guam</t>
+  </si>
+  <si>
+    <t>MHL</t>
+  </si>
+  <si>
+    <t>Marshall Islands</t>
+  </si>
+  <si>
+    <t>MNP</t>
+  </si>
+  <si>
+    <t>Northern Mariana Islands</t>
+  </si>
+  <si>
+    <t>PLW</t>
+  </si>
+  <si>
+    <t>Palau</t>
+  </si>
+  <si>
+    <t>PHL</t>
+  </si>
+  <si>
+    <t>Phillipines</t>
+  </si>
+  <si>
+    <t>PRI</t>
+  </si>
+  <si>
+    <t>Puerto Rico</t>
+  </si>
+  <si>
+    <t>UMI</t>
+  </si>
+  <si>
+    <t>U.S. Minor Outlying Islands</t>
+  </si>
+  <si>
+    <t>VIR</t>
+  </si>
+  <si>
+    <t>Virgin Islands</t>
+  </si>
+  <si>
+    <t>urn:undefined</t>
   </si>
 </sst>
 </file>
@@ -607,83 +677,83 @@
         <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>10</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>12</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>14</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>16</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>18</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>20</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>22</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>26</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -702,658 +772,792 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>38</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>40</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>42</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>49</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>50</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>66</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>67</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>78</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>80</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>81</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>82</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>85</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>87</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>90</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>92</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>93</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>94</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>95</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>96</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>98</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>99</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>109</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>111</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>113</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>114</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>117</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>119</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>123</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>127</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>131</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>135</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B82" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="B82" t="s" s="2">
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>138</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -7,8 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from 200-.1215" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from unknown" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from unknown" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from 200-.1215" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +82,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Navigate to [ConceptMap VF_PractitionerCountry](ConceptMap-CMVFPractitionerCountry.html)</t>
+    <t>Navigate to [ConceptMap VF_PractitionerCountry](ConceptMap-CMVFPractitionerCountry.html)
+&gt; Note that the FHIR binding is to the codes in the fhir system. The codes from the VistADefinedElements system are map source codes: they may be included in addition to the fhir codes, but they don't address the binding requirement.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,6 +101,84 @@
     <t>Concept</t>
   </si>
   <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>ASM</t>
+  </si>
+  <si>
+    <t>American Samoa</t>
+  </si>
+  <si>
+    <t>FSM</t>
+  </si>
+  <si>
+    <t>Federated States of Micronesia</t>
+  </si>
+  <si>
+    <t>GUM</t>
+  </si>
+  <si>
+    <t>Guam</t>
+  </si>
+  <si>
+    <t>MHL</t>
+  </si>
+  <si>
+    <t>Marshall Islands</t>
+  </si>
+  <si>
+    <t>MNP</t>
+  </si>
+  <si>
+    <t>Northern Mariana Islands</t>
+  </si>
+  <si>
+    <t>PLW</t>
+  </si>
+  <si>
+    <t>Palau</t>
+  </si>
+  <si>
+    <t>PHL</t>
+  </si>
+  <si>
+    <t>Phillipines</t>
+  </si>
+  <si>
+    <t>PRI</t>
+  </si>
+  <si>
+    <t>Puerto Rico</t>
+  </si>
+  <si>
+    <t>UMI</t>
+  </si>
+  <si>
+    <t>U.S. Minor Outlying Islands</t>
+  </si>
+  <si>
+    <t>VIR</t>
+  </si>
+  <si>
+    <t>Virgin Islands</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>urn:undefined</t>
+  </si>
+  <si>
     <t>ALABAMA</t>
   </si>
   <si>
@@ -421,85 +500,7 @@
     <t>YUKON TERRITORY</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
     <t>http://va.gov/terminology/vistaDefinedElements/200-.1215</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
-    <t>ASM</t>
-  </si>
-  <si>
-    <t>American Samoa</t>
-  </si>
-  <si>
-    <t>FSM</t>
-  </si>
-  <si>
-    <t>Federated States of Micronesia</t>
-  </si>
-  <si>
-    <t>GUM</t>
-  </si>
-  <si>
-    <t>Guam</t>
-  </si>
-  <si>
-    <t>MHL</t>
-  </si>
-  <si>
-    <t>Marshall Islands</t>
-  </si>
-  <si>
-    <t>MNP</t>
-  </si>
-  <si>
-    <t>Northern Mariana Islands</t>
-  </si>
-  <si>
-    <t>PLW</t>
-  </si>
-  <si>
-    <t>Palau</t>
-  </si>
-  <si>
-    <t>PHL</t>
-  </si>
-  <si>
-    <t>Phillipines</t>
-  </si>
-  <si>
-    <t>PRI</t>
-  </si>
-  <si>
-    <t>Puerto Rico</t>
-  </si>
-  <si>
-    <t>UMI</t>
-  </si>
-  <si>
-    <t>U.S. Minor Outlying Islands</t>
-  </si>
-  <si>
-    <t>VIR</t>
-  </si>
-  <si>
-    <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>urn:undefined</t>
   </si>
 </sst>
 </file>
@@ -763,6 +764,140 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -780,783 +915,649 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>43</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>45</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>46</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>59</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>60</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>61</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>62</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>63</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>66</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>67</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>68</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>69</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>71</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>73</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>74</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>75</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>78</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>80</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>84</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>86</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>87</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>89</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>93</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>95</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>97</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>99</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>100</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>101</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>102</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>103</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>104</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>105</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>106</v>
+        <v>132</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>108</v>
+        <v>134</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>110</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>113</v>
+        <v>139</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>114</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>116</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>118</v>
+        <v>144</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>119</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>120</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>122</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>123</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>124</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>126</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>127</v>
+        <v>153</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>128</v>
+        <v>154</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>130</v>
+        <v>156</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>131</v>
+        <v>157</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>132</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>134</v>
+        <v>160</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>135</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>137</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="B15" t="s" s="2">
         <v>161</v>
       </c>
     </row>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="161">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,10 +82,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Navigate to [ConceptMap VF_PractitionerCountry](ConceptMap-CMVFPractitionerCountry.html)
-&gt; Note that the FHIR binding is to the codes in the fhir system. The codes from the VistADefinedElements system are map source codes: they may be included in addition to the fhir codes, but they don't address the binding requirement.</t>
-  </si>
-  <si>
     <t>Purpose</t>
   </si>
   <si>
@@ -500,7 +496,7 @@
     <t>YUKON TERRITORY</t>
   </si>
   <si>
-    <t>http://va.gov/terminology/vistaDefinedElements/200-.1215</t>
+    <t>http://va.gov/terminology/vistaDefinedTerms/200-.1215</t>
   </si>
 </sst>
 </file>
@@ -733,28 +729,26 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" t="s" s="2">
-        <v>22</v>
-      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -773,7 +767,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -781,7 +775,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>20</v>
@@ -789,106 +783,106 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>35</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>39</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>41</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>43</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>49</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -907,7 +901,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -915,650 +909,650 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>63</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>65</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>67</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>74</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>76</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>92</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>103</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>104</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>106</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>110</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>112</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>115</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>117</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>119</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>121</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>123</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B54" t="s" s="2">
         <v>124</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>125</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>134</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>136</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>139</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>142</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>144</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>148</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>152</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>156</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>160</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="162">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>ValueSet for terminology map VF_PractitionerCountry</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -729,26 +732,28 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -767,7 +772,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -775,7 +780,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>20</v>
@@ -783,106 +788,106 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -901,7 +906,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -909,650 +914,650 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +82,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet for terminology map VF_PractitionerCountry</t>
+    <t>ValueSet for Terminology Maps VF_PractitionerCountry</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from unknown" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from string" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -174,7 +174,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>urn:undefined</t>
+    <t>http://hl7.org/fhir/StructureDefinition/string</t>
   </si>
 </sst>
 </file>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from string" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFPractitionerCountry.xlsx
+++ b/docs/ValueSet-VSVFPractitionerCountry.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
